--- a/employee_incident_report_forms/022_defective_product_log_form--employee_incident_report_forms.xlsx
+++ b/employee_incident_report_forms/022_defective_product_log_form--employee_incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category (2)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Status (2)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>product_id</t>
+          <t>product_id_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Product ID</t>
+          <t>Product Id 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>category_id</t>
+          <t>category_id_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category Id 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>status_id</t>
+          <t>status_id_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Status Id 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,46 +1165,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_id_choices</t>
+          <t>status_id_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_id_choices</t>
+          <t>status_id_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,80 +1216,80 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>status_id_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>cat1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Cat1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>status_id_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>cat2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Cat2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>status_id_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>cat3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Cat3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>status_id_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>cat4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Cat4</t>
         </is>
       </c>
     </row>
@@ -1301,80 +1301,80 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>cat1</t>
+          <t>cat5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cat1</t>
+          <t>Cat5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cat2</t>
+          <t>stat1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cat2</t>
+          <t>Stat1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cat3</t>
+          <t>stat2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cat3</t>
+          <t>Stat2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cat4</t>
+          <t>stat3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cat4</t>
+          <t>Stat3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cat5</t>
+          <t>stat4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cat5</t>
+          <t>Stat4</t>
         </is>
       </c>
     </row>
@@ -1386,80 +1386,80 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>stat1</t>
+          <t>stat5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Stat1</t>
+          <t>Stat5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>product_type_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>stat2</t>
+          <t>prod1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stat2</t>
+          <t>Prod1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>product_type_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>stat3</t>
+          <t>prod2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Stat3</t>
+          <t>Prod2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>product_type_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>stat4</t>
+          <t>prod3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Stat4</t>
+          <t>Prod3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>product_type_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>stat5</t>
+          <t>prod4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Stat5</t>
+          <t>Prod4</t>
         </is>
       </c>
     </row>
@@ -1471,80 +1471,80 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>prod1</t>
+          <t>prod5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prod1</t>
+          <t>Prod5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>product_type_choices</t>
+          <t>product_model_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>prod2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prod2</t>
+          <t>Model1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>product_type_choices</t>
+          <t>product_model_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>prod3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Prod3</t>
+          <t>Model2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>product_type_choices</t>
+          <t>product_model_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>prod4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Prod4</t>
+          <t>Model3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>product_type_choices</t>
+          <t>product_model_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prod5</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Prod5</t>
+          <t>Model4</t>
         </is>
       </c>
     </row>
@@ -1556,80 +1556,80 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Model1</t>
+          <t>Model5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>product_model_choices</t>
+          <t>product_version_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>version1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Model2</t>
+          <t>Version1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>product_model_choices</t>
+          <t>product_version_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>version2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Model3</t>
+          <t>Version2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>product_model_choices</t>
+          <t>product_version_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>version3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Model4</t>
+          <t>Version3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>product_model_choices</t>
+          <t>product_version_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>model5</t>
+          <t>version4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Model5</t>
+          <t>Version4</t>
         </is>
       </c>
     </row>
@@ -1641,250 +1641,148 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>version1</t>
+          <t>version5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Version1</t>
+          <t>Version5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>product_version_choices</t>
+          <t>category_id_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>version2</t>
+          <t>cat1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Version2</t>
+          <t>Cat1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>product_version_choices</t>
+          <t>category_id_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>version3</t>
+          <t>cat2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Version3</t>
+          <t>Cat2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>product_version_choices</t>
+          <t>category_id_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>version4</t>
+          <t>cat3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Version4</t>
+          <t>Cat3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>product_version_choices</t>
+          <t>category_id_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>version5</t>
+          <t>cat4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Version5</t>
+          <t>Cat4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>category_id_choices</t>
+          <t>category_id_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>cat1</t>
+          <t>cat5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cat1</t>
+          <t>Cat5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>category_id_choices</t>
+          <t>status_id_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>cat2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cat2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>category_id_choices</t>
+          <t>status_id_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>cat3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cat3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>category_id_choices</t>
+          <t>status_id_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>cat4</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cat4</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>category_id_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>cat5</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Cat5</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>status_id_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>status_id_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>status_id_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>status_id_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>status_id_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
